--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="237">
   <si>
     <t>Mat</t>
   </si>
@@ -85,21 +85,90 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>AYALA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
     <t>CUATRA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -112,37 +181,70 @@
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CHONKOA</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERIAÑEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
   </si>
   <si>
     <t>CANTE</t>
@@ -163,9 +265,6 @@
     <t>PARRA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -178,75 +277,6 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
     <t>CERON</t>
   </si>
   <si>
@@ -262,6 +292,45 @@
     <t>RIVERA</t>
   </si>
   <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
@@ -271,37 +340,61 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
     <t>SERRANO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
+    <t>------</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>FELIPE</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>CADENA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>COLMENARES</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>MERLIN</t>
+  </si>
+  <si>
+    <t>MONTES</t>
   </si>
   <si>
     <t>VALDEZ</t>
@@ -322,66 +415,6 @@
     <t>PAZ</t>
   </si>
   <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>FELIPE</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>MERLIN</t>
-  </si>
-  <si>
-    <t>MONTES</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
@@ -403,6 +436,102 @@
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>LEONEL FELIPE</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>LUIS JAVIER</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>ZAID RAUL</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>QUETZALY</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>ESTEPHANY</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
     <t>MARCO</t>
   </si>
   <si>
@@ -421,9 +550,6 @@
     <t>HECTOR ALAN</t>
   </si>
   <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
     <t>ERIK OMAR</t>
   </si>
   <si>
@@ -436,46 +562,100 @@
     <t>OSMAR</t>
   </si>
   <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>ZAID RAUL</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>QUETZALY</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>YAZMIN SINAI</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>JULISSA</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>SAIRA</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>ELIDA CITLALI</t>
+  </si>
+  <si>
+    <t>KARYME CONCEPCION</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>ROSARIO DE JESUS</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>ALAN SANTIAGO</t>
+  </si>
+  <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>DEMY</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>MARIELA</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>ARAWY</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>AMERICA</t>
+  </si>
+  <si>
+    <t>ANDREA JANETH</t>
+  </si>
+  <si>
+    <t>ESTRELLA SARAHI</t>
+  </si>
+  <si>
+    <t>CRISTIAN LEOBARDO</t>
   </si>
   <si>
     <t>TOMAS RAFAEL</t>
@@ -529,118 +709,10 @@
     <t>ZABDIEL</t>
   </si>
   <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>YAZMIN SINAI</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>SAIRA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>ELIDA CITLALI</t>
-  </si>
-  <si>
-    <t>KARYME CONCEPCION</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ROSARIO DE JESUS</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>ALAN SANTIAGO</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>DEMY</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>ARAWY</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>AMERICA</t>
-  </si>
-  <si>
-    <t>ANDREA JANETH</t>
-  </si>
-  <si>
-    <t>ESTRELLA SARAHI</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
-  </si>
-  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
     <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
   <si>
     <t>JOSE LUIS</t>
@@ -1475,7 +1547,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1507,16 +1579,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920177</v>
+        <v>22330051920184</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1530,16 +1602,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920179</v>
+        <v>22330051920378</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1553,16 +1625,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920183</v>
+        <v>22330051920200</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1576,16 +1648,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920185</v>
+        <v>22330051920371</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1599,16 +1671,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920188</v>
+        <v>22330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1622,22 +1694,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920187</v>
+        <v>22330051920262</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1645,22 +1717,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920378</v>
+        <v>22330051920264</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1668,22 +1740,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920192</v>
+        <v>22330051920265</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1691,19 +1763,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920197</v>
+        <v>22330051920268</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1711,22 +1786,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920358</v>
+        <v>22330051920270</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1734,22 +1809,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920363</v>
+        <v>22330051920273</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1757,22 +1832,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920200</v>
+        <v>22330051920285</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1780,22 +1855,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920371</v>
+        <v>22330051920286</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1803,16 +1878,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920262</v>
+        <v>22330051920288</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1826,22 +1901,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920264</v>
+        <v>22330051920362</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1849,22 +1924,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920265</v>
+        <v>22330051920394</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1872,22 +1947,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920268</v>
+        <v>22330051920290</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1895,22 +1970,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920270</v>
+        <v>22330051920291</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1918,22 +1993,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920273</v>
+        <v>22330051920294</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1941,22 +2016,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920285</v>
+        <v>22330051920412</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1964,22 +2039,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920286</v>
+        <v>22330051920297</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1987,22 +2062,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920288</v>
+        <v>22330051920298</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2010,22 +2085,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920362</v>
+        <v>22330051920302</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -2033,22 +2108,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920394</v>
+        <v>22330051920303</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2056,16 +2131,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920291</v>
+        <v>22330051920419</v>
       </c>
       <c r="B26" t="s">
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -2079,16 +2154,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920293</v>
+        <v>22330051920308</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -2102,16 +2177,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920295</v>
+        <v>22330051920312</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -2125,16 +2200,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920360</v>
+        <v>22330051920364</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -2148,16 +2223,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920415</v>
+        <v>22330051920397</v>
       </c>
       <c r="B30" t="s">
         <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -2171,22 +2246,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920300</v>
+        <v>21330051920121</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2194,22 +2269,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920301</v>
+        <v>21330051920122</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -2217,22 +2292,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920304</v>
+        <v>18330051920377</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2240,22 +2315,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920305</v>
+        <v>20330051920152</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -2263,312 +2338,312 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920306</v>
+        <v>22330051920177</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920307</v>
+        <v>22330051920179</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920309</v>
+        <v>22330051920183</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>22330051920310</v>
+        <v>22330051920185</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>22330051920311</v>
+        <v>22330051920188</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="C39" t="s">
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>22330051920313</v>
+        <v>22330051920187</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>22330051920370</v>
+        <v>22330051920192</v>
       </c>
       <c r="B41" t="s">
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>22330051920314</v>
+        <v>22330051920197</v>
       </c>
       <c r="B42" t="s">
         <v>51</v>
       </c>
-      <c r="C42" t="s">
-        <v>100</v>
-      </c>
       <c r="D42" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>22330051920315</v>
+        <v>22330051920358</v>
       </c>
       <c r="B43" t="s">
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>21330051920121</v>
+        <v>22330051920363</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D44" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>21330051920122</v>
+        <v>22330051920409</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="D45" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>18330051920377</v>
+        <v>22330051920411</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>20330051920152</v>
+        <v>22330051920266</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>22330051920409</v>
+        <v>22330051920271</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
@@ -2582,16 +2657,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>22330051920411</v>
+        <v>22330051920272</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
@@ -2605,16 +2680,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>22330051920266</v>
+        <v>22330051920406</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
@@ -2628,22 +2703,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>22330051920271</v>
+        <v>21330051920002</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D51" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2651,22 +2726,22 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>22330051920272</v>
+        <v>22330051920392</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="D52" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -2674,22 +2749,22 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>22330051920406</v>
+        <v>22330051920205</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D53" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2697,16 +2772,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>21330051920002</v>
+        <v>22330051920207</v>
       </c>
       <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" t="s">
         <v>59</v>
       </c>
-      <c r="C54" t="s">
-        <v>107</v>
-      </c>
       <c r="D54" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
@@ -2720,16 +2795,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>22330051920392</v>
+        <v>22330051920393</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="D55" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
@@ -2743,16 +2818,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>22330051920205</v>
+        <v>22330051920420</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D56" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -2766,16 +2841,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>22330051920207</v>
+        <v>22330051920211</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
@@ -2789,16 +2864,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>22330051920393</v>
+        <v>22330051920423</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
@@ -2812,16 +2887,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>22330051920420</v>
+        <v>22330051920374</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -2835,16 +2910,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>22330051920211</v>
+        <v>22330051920214</v>
       </c>
       <c r="B60" t="s">
         <v>63</v>
       </c>
       <c r="C60" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D60" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
@@ -2858,16 +2933,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>22330051920423</v>
+        <v>22330051920215</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="D61" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
@@ -2881,16 +2956,16 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>22330051920374</v>
+        <v>20322051180081</v>
       </c>
       <c r="B62" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C62" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="D62" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -2904,16 +2979,16 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>22330051920214</v>
+        <v>22330051920216</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C63" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
@@ -2927,16 +3002,16 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>22330051920215</v>
+        <v>22330051920218</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C64" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="D64" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -2950,16 +3025,16 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>20322051180081</v>
+        <v>22330051920217</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="D65" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
@@ -2973,16 +3048,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>22330051920216</v>
+        <v>22330051920219</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D66" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
@@ -2996,16 +3071,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>22330051920218</v>
+        <v>22330051920220</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
@@ -3019,16 +3094,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>22330051920217</v>
+        <v>22330051920221</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C68" t="s">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="D68" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
@@ -3042,16 +3117,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>22330051920219</v>
+        <v>22330051920222</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="D69" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E69" t="s">
         <v>9</v>
@@ -3065,16 +3140,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>22330051920220</v>
+        <v>22330051920223</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="D70" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
@@ -3088,16 +3163,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>22330051920221</v>
+        <v>22330051920421</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D71" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
@@ -3111,16 +3186,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>22330051920222</v>
+        <v>22330051920224</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C72" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="D72" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -3134,16 +3209,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>22330051920223</v>
+        <v>22330051920225</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D73" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
@@ -3157,16 +3232,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>22330051920421</v>
+        <v>22330051920226</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C74" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="D74" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -3180,16 +3255,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>22330051920224</v>
+        <v>22330051920228</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="C75" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="D75" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -3203,16 +3278,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>22330051920225</v>
+        <v>22330051920227</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D76" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -3226,16 +3301,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>22330051920226</v>
+        <v>22330051920229</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
@@ -3249,22 +3324,22 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>22330051920228</v>
+        <v>22330051920293</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3272,22 +3347,22 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>22330051920227</v>
+        <v>22330051920295</v>
       </c>
       <c r="B79" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3295,22 +3370,22 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>22330051920229</v>
+        <v>22330051920360</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3318,22 +3393,22 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>21330051920114</v>
+        <v>22330051920415</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="D81" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3341,22 +3416,22 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>21330051920116</v>
+        <v>22330051920300</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="D82" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3364,22 +3439,22 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>21330051920118</v>
+        <v>22330051920301</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D83" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -3387,22 +3462,22 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>20330051920266</v>
+        <v>22330051920304</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="D84" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="E84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -3410,22 +3485,22 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>21330051920123</v>
+        <v>22330051920305</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3433,19 +3508,22 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>21330051920129</v>
+        <v>22330051920306</v>
+      </c>
+      <c r="B86" t="s">
+        <v>29</v>
       </c>
       <c r="C86" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="D86" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3453,22 +3531,22 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>21330051920131</v>
+        <v>22330051920307</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D87" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -3476,24 +3554,340 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
+        <v>22330051920309</v>
+      </c>
+      <c r="B88" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" t="s">
+        <v>88</v>
+      </c>
+      <c r="D88" t="s">
+        <v>223</v>
+      </c>
+      <c r="E88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>22330051920310</v>
+      </c>
+      <c r="B89" t="s">
+        <v>68</v>
+      </c>
+      <c r="C89" t="s">
+        <v>129</v>
+      </c>
+      <c r="D89" t="s">
+        <v>224</v>
+      </c>
+      <c r="E89" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>22330051920311</v>
+      </c>
+      <c r="B90" t="s">
+        <v>51</v>
+      </c>
+      <c r="D90" t="s">
+        <v>225</v>
+      </c>
+      <c r="E90" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>22330051920313</v>
+      </c>
+      <c r="B91" t="s">
+        <v>82</v>
+      </c>
+      <c r="C91" t="s">
+        <v>130</v>
+      </c>
+      <c r="D91" t="s">
+        <v>226</v>
+      </c>
+      <c r="E91" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>22330051920370</v>
+      </c>
+      <c r="B92" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" t="s">
+        <v>40</v>
+      </c>
+      <c r="D92" t="s">
+        <v>227</v>
+      </c>
+      <c r="E92" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>22330051920314</v>
+      </c>
+      <c r="B93" t="s">
+        <v>84</v>
+      </c>
+      <c r="C93" t="s">
+        <v>131</v>
+      </c>
+      <c r="D93" t="s">
+        <v>228</v>
+      </c>
+      <c r="E93" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
+        <v>22330051920315</v>
+      </c>
+      <c r="B94" t="s">
+        <v>85</v>
+      </c>
+      <c r="C94" t="s">
+        <v>95</v>
+      </c>
+      <c r="D94" t="s">
+        <v>229</v>
+      </c>
+      <c r="E94" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95">
+        <v>21330051920114</v>
+      </c>
+      <c r="B95" t="s">
+        <v>86</v>
+      </c>
+      <c r="C95" t="s">
+        <v>132</v>
+      </c>
+      <c r="D95" t="s">
+        <v>230</v>
+      </c>
+      <c r="E95" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96">
+        <v>21330051920116</v>
+      </c>
+      <c r="B96" t="s">
+        <v>87</v>
+      </c>
+      <c r="C96" t="s">
+        <v>133</v>
+      </c>
+      <c r="D96" t="s">
+        <v>231</v>
+      </c>
+      <c r="E96" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97">
+        <v>21330051920118</v>
+      </c>
+      <c r="B97" t="s">
+        <v>88</v>
+      </c>
+      <c r="C97" t="s">
+        <v>134</v>
+      </c>
+      <c r="D97" t="s">
+        <v>163</v>
+      </c>
+      <c r="E97" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98">
+        <v>20330051920266</v>
+      </c>
+      <c r="B98" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98" t="s">
+        <v>135</v>
+      </c>
+      <c r="D98" t="s">
+        <v>232</v>
+      </c>
+      <c r="E98" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99">
+        <v>21330051920123</v>
+      </c>
+      <c r="B99" t="s">
+        <v>89</v>
+      </c>
+      <c r="C99" t="s">
+        <v>136</v>
+      </c>
+      <c r="D99" t="s">
+        <v>233</v>
+      </c>
+      <c r="E99" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" t="s">
+        <v>15</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100">
+        <v>21330051920129</v>
+      </c>
+      <c r="C100" t="s">
+        <v>137</v>
+      </c>
+      <c r="D100" t="s">
+        <v>234</v>
+      </c>
+      <c r="E100" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" t="s">
+        <v>15</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101">
+        <v>21330051920131</v>
+      </c>
+      <c r="B101" t="s">
+        <v>70</v>
+      </c>
+      <c r="C101" t="s">
+        <v>122</v>
+      </c>
+      <c r="D101" t="s">
+        <v>235</v>
+      </c>
+      <c r="E101" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" t="s">
+        <v>15</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102">
         <v>21330051920132</v>
       </c>
-      <c r="B88" t="s">
-        <v>80</v>
-      </c>
-      <c r="C88" t="s">
-        <v>127</v>
-      </c>
-      <c r="D88" t="s">
-        <v>212</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="B102" t="s">
+        <v>90</v>
+      </c>
+      <c r="C102" t="s">
+        <v>138</v>
+      </c>
+      <c r="D102" t="s">
+        <v>236</v>
+      </c>
+      <c r="E102" t="s">
         <v>10</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F102" t="s">
         <v>15</v>
       </c>
-      <c r="G88">
+      <c r="G102">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="242">
   <si>
     <t>Mat</t>
   </si>
@@ -112,6 +112,15 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -265,9 +274,6 @@
     <t>PARRA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -304,12 +310,15 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>VALLEJO</t>
   </si>
   <si>
@@ -467,6 +476,12 @@
   </si>
   <si>
     <t>JOSE</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
   </si>
   <si>
     <t>QUETZALY</t>
@@ -1547,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1585,10 +1600,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1608,10 +1623,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1631,10 +1646,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1657,7 +1672,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1677,10 +1692,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1700,10 +1715,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1723,10 +1738,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1746,10 +1761,10 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1772,7 +1787,7 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1792,10 +1807,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1815,10 +1830,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1832,16 +1847,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920285</v>
+        <v>22330051920276</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1855,16 +1870,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920286</v>
+        <v>22330051920407</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1878,16 +1893,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920288</v>
+        <v>22330051920282</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1901,22 +1916,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920362</v>
+        <v>22330051920285</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1924,22 +1939,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920394</v>
+        <v>22330051920286</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1947,22 +1962,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920290</v>
+        <v>22330051920288</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1970,22 +1985,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920291</v>
+        <v>22330051920362</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1993,22 +2008,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920294</v>
+        <v>22330051920394</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -2016,16 +2031,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920412</v>
+        <v>22330051920290</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -2039,16 +2054,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920297</v>
+        <v>22330051920291</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -2062,16 +2077,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920298</v>
+        <v>22330051920294</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -2085,16 +2100,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920302</v>
+        <v>22330051920412</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -2108,16 +2123,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920303</v>
+        <v>22330051920297</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -2131,16 +2146,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920419</v>
+        <v>22330051920298</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -2154,16 +2169,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920308</v>
+        <v>22330051920302</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -2177,16 +2192,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920312</v>
+        <v>22330051920303</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -2200,16 +2215,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920364</v>
+        <v>22330051920419</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -2223,16 +2238,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920397</v>
+        <v>22330051920308</v>
       </c>
       <c r="B30" t="s">
         <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -2246,22 +2261,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920121</v>
+        <v>22330051920312</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2269,22 +2284,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920122</v>
+        <v>22330051920364</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -2292,22 +2307,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>18330051920377</v>
+        <v>22330051920397</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2315,16 +2330,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920152</v>
+        <v>21330051920121</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -2338,30 +2353,30 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920177</v>
+        <v>21330051920122</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920179</v>
+        <v>18330051920377</v>
       </c>
       <c r="B36" t="s">
         <v>49</v>
@@ -2370,53 +2385,53 @@
         <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920183</v>
+        <v>20330051920152</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>22330051920185</v>
+        <v>22330051920177</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2430,16 +2445,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>22330051920188</v>
+        <v>22330051920179</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2453,16 +2468,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>22330051920187</v>
+        <v>22330051920183</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2476,16 +2491,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>22330051920192</v>
+        <v>22330051920185</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2499,13 +2514,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>22330051920197</v>
+        <v>22330051920188</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="C42" t="s">
+        <v>109</v>
       </c>
       <c r="D42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2519,16 +2537,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>22330051920358</v>
+        <v>22330051920187</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2542,16 +2560,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>22330051920363</v>
+        <v>22330051920192</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2565,22 +2583,19 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>22330051920409</v>
+        <v>22330051920197</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2588,22 +2603,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>22330051920411</v>
+        <v>22330051920358</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2611,22 +2626,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>22330051920266</v>
+        <v>22330051920363</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2634,16 +2649,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>22330051920271</v>
+        <v>22330051920409</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="D48" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
@@ -2657,16 +2672,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>22330051920272</v>
+        <v>22330051920411</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
@@ -2680,16 +2695,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>22330051920406</v>
+        <v>22330051920266</v>
       </c>
       <c r="B50" t="s">
         <v>57</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
@@ -2703,22 +2718,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>21330051920002</v>
+        <v>22330051920271</v>
       </c>
       <c r="B51" t="s">
         <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="D51" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2726,22 +2741,22 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>22330051920392</v>
+        <v>22330051920272</v>
       </c>
       <c r="B52" t="s">
         <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="D52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -2749,22 +2764,22 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>22330051920205</v>
+        <v>22330051920406</v>
       </c>
       <c r="B53" t="s">
         <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D53" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2772,16 +2787,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>22330051920207</v>
+        <v>21330051920002</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="D54" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
@@ -2795,16 +2810,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>22330051920393</v>
+        <v>22330051920392</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="D55" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
@@ -2818,16 +2833,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>22330051920420</v>
+        <v>22330051920205</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C56" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -2841,16 +2856,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>22330051920211</v>
+        <v>22330051920207</v>
       </c>
       <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" t="s">
         <v>62</v>
       </c>
-      <c r="C57" t="s">
-        <v>116</v>
-      </c>
       <c r="D57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
@@ -2864,16 +2879,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>22330051920423</v>
+        <v>22330051920393</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
         <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
@@ -2887,16 +2902,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>22330051920374</v>
+        <v>22330051920420</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
         <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -2910,16 +2925,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>22330051920214</v>
+        <v>22330051920211</v>
       </c>
       <c r="B60" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C60" t="s">
         <v>119</v>
       </c>
       <c r="D60" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
@@ -2933,16 +2948,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>22330051920215</v>
+        <v>22330051920423</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C61" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D61" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
@@ -2956,16 +2971,16 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>20322051180081</v>
+        <v>22330051920374</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C62" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -2979,16 +2994,16 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>22330051920216</v>
+        <v>22330051920214</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
@@ -3002,16 +3017,16 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>22330051920218</v>
+        <v>22330051920215</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -3025,16 +3040,16 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>22330051920217</v>
+        <v>20322051180081</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C65" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
@@ -3048,16 +3063,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>22330051920219</v>
+        <v>22330051920216</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
@@ -3071,16 +3086,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>22330051920220</v>
+        <v>22330051920218</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
@@ -3094,16 +3109,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>22330051920221</v>
+        <v>22330051920217</v>
       </c>
       <c r="B68" t="s">
         <v>69</v>
       </c>
       <c r="C68" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="D68" t="s">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
@@ -3117,16 +3132,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>22330051920222</v>
+        <v>22330051920219</v>
       </c>
       <c r="B69" t="s">
         <v>70</v>
       </c>
       <c r="C69" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E69" t="s">
         <v>9</v>
@@ -3140,16 +3155,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>22330051920223</v>
+        <v>22330051920220</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
@@ -3163,16 +3178,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>22330051920421</v>
+        <v>22330051920221</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
@@ -3186,16 +3201,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>22330051920224</v>
+        <v>22330051920222</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C72" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="D72" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -3209,16 +3224,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>22330051920225</v>
+        <v>22330051920223</v>
       </c>
       <c r="B73" t="s">
         <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D73" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
@@ -3232,16 +3247,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>22330051920226</v>
+        <v>22330051920421</v>
       </c>
       <c r="B74" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D74" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -3255,16 +3270,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>22330051920228</v>
+        <v>22330051920224</v>
       </c>
       <c r="B75" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D75" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -3278,16 +3293,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>22330051920227</v>
+        <v>22330051920225</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -3301,16 +3316,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>22330051920229</v>
+        <v>22330051920226</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D77" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
@@ -3324,22 +3339,22 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>22330051920293</v>
+        <v>22330051920228</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C78" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3347,22 +3362,22 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>22330051920295</v>
+        <v>22330051920227</v>
       </c>
       <c r="B79" t="s">
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="D79" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3370,22 +3385,22 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>22330051920360</v>
+        <v>22330051920229</v>
       </c>
       <c r="B80" t="s">
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="D80" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3393,16 +3408,16 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>22330051920415</v>
+        <v>22330051920293</v>
       </c>
       <c r="B81" t="s">
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
@@ -3416,16 +3431,16 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>22330051920300</v>
+        <v>22330051920295</v>
       </c>
       <c r="B82" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D82" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
@@ -3439,16 +3454,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>22330051920301</v>
+        <v>22330051920360</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
@@ -3462,16 +3477,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>22330051920304</v>
+        <v>22330051920415</v>
       </c>
       <c r="B84" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D84" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
@@ -3485,16 +3500,16 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>22330051920305</v>
+        <v>22330051920300</v>
       </c>
       <c r="B85" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D85" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -3508,16 +3523,16 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>22330051920306</v>
+        <v>22330051920301</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C86" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
@@ -3531,16 +3546,16 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>22330051920307</v>
+        <v>22330051920304</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="C87" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="D87" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -3554,16 +3569,16 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>22330051920309</v>
+        <v>22330051920305</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C88" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="D88" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -3577,16 +3592,16 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>22330051920310</v>
+        <v>22330051920306</v>
       </c>
       <c r="B89" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="D89" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
@@ -3600,13 +3615,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>22330051920311</v>
+        <v>22330051920307</v>
       </c>
       <c r="B90" t="s">
-        <v>51</v>
+        <v>83</v>
+      </c>
+      <c r="C90" t="s">
+        <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -3620,16 +3638,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>22330051920313</v>
+        <v>22330051920309</v>
       </c>
       <c r="B91" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
@@ -3643,16 +3661,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>22330051920370</v>
+        <v>22330051920310</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
@@ -3666,16 +3684,13 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>22330051920314</v>
+        <v>22330051920311</v>
       </c>
       <c r="B93" t="s">
-        <v>84</v>
-      </c>
-      <c r="C93" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="D93" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
@@ -3689,16 +3704,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>22330051920315</v>
+        <v>22330051920313</v>
       </c>
       <c r="B94" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="D94" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
@@ -3712,22 +3727,22 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>21330051920114</v>
+        <v>22330051920370</v>
       </c>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="D95" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -3735,22 +3750,22 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>21330051920116</v>
+        <v>22330051920314</v>
       </c>
       <c r="B96" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C96" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -3758,22 +3773,22 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>21330051920118</v>
+        <v>22330051920315</v>
       </c>
       <c r="B97" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D97" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
       <c r="E97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -3781,16 +3796,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>20330051920266</v>
+        <v>21330051920114</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="C98" t="s">
         <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
@@ -3804,7 +3819,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>21330051920123</v>
+        <v>21330051920116</v>
       </c>
       <c r="B99" t="s">
         <v>89</v>
@@ -3813,7 +3828,7 @@
         <v>136</v>
       </c>
       <c r="D99" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
@@ -3827,13 +3842,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>21330051920129</v>
+        <v>21330051920118</v>
+      </c>
+      <c r="B100" t="s">
+        <v>90</v>
       </c>
       <c r="C100" t="s">
         <v>137</v>
       </c>
       <c r="D100" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -3847,16 +3865,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>21330051920131</v>
+        <v>20330051920266</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="C101" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D101" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
@@ -3870,16 +3888,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>21330051920132</v>
+        <v>21330051920123</v>
       </c>
       <c r="B102" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C102" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -3888,6 +3906,72 @@
         <v>15</v>
       </c>
       <c r="G102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103">
+        <v>21330051920129</v>
+      </c>
+      <c r="C103" t="s">
+        <v>140</v>
+      </c>
+      <c r="D103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E103" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" t="s">
+        <v>15</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104">
+        <v>21330051920131</v>
+      </c>
+      <c r="B104" t="s">
+        <v>73</v>
+      </c>
+      <c r="C104" t="s">
+        <v>125</v>
+      </c>
+      <c r="D104" t="s">
+        <v>240</v>
+      </c>
+      <c r="E104" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105">
+        <v>21330051920132</v>
+      </c>
+      <c r="B105" t="s">
+        <v>92</v>
+      </c>
+      <c r="C105" t="s">
+        <v>141</v>
+      </c>
+      <c r="D105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E105" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -875,10 +875,10 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -1035,7 +1035,7 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1198,10 +1198,10 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>9</v>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="111">
   <si>
     <t>Mat</t>
   </si>
@@ -97,112 +97,142 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CADENA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
   </si>
   <si>
     <t>CARBAJAL</t>
@@ -211,48 +241,6 @@
     <t>CORTES</t>
   </si>
   <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
@@ -271,19 +259,64 @@
     <t>SERGIO IVAN</t>
   </si>
   <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>ALDO</t>
   </si>
   <si>
     <t>QUETZALY</t>
   </si>
   <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
   </si>
   <si>
     <t>LUIS GUSTAVO</t>
@@ -304,64 +337,10 @@
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
-    <t>DIEGO</t>
+    <t>JOSUE ISRAEL</t>
   </si>
   <si>
     <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -820,10 +799,10 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -832,7 +811,7 @@
         <v>22</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H4">
         <v>6.8</v>
@@ -983,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>33</v>
@@ -1143,10 +1122,10 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -1155,7 +1134,7 @@
         <v>22</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -1220,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1261,7 +1240,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1281,10 +1260,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1304,10 +1283,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1327,10 +1306,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1344,16 +1323,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920270</v>
+        <v>22330051920367</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1373,10 +1352,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1390,22 +1369,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920282</v>
+        <v>22330051920362</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1413,22 +1392,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920285</v>
+        <v>22330051920394</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1436,22 +1415,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920362</v>
+        <v>22330051920419</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1459,22 +1438,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920394</v>
+        <v>22330051920312</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1482,16 +1461,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920294</v>
+        <v>22330051920397</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1505,22 +1484,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920412</v>
+        <v>20330051920152</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1528,275 +1507,275 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920297</v>
+        <v>22330051920177</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920298</v>
+        <v>22330051920188</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920302</v>
+        <v>22330051920187</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920303</v>
+        <v>22330051920192</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920419</v>
+        <v>22330051920363</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920308</v>
+        <v>22330051920409</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920312</v>
+        <v>22330051920411</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
         <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920397</v>
+        <v>22330051920272</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920122</v>
+        <v>22330051920285</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>18330051920377</v>
+        <v>21330051920002</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920152</v>
+        <v>22330051920205</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920177</v>
+        <v>22330051920423</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1804,22 +1783,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920188</v>
+        <v>22330051920374</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1827,22 +1806,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920187</v>
+        <v>22330051920222</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1850,22 +1829,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920192</v>
+        <v>22330051920294</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1873,22 +1852,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920363</v>
+        <v>22330051920412</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1896,22 +1875,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920409</v>
+        <v>22330051920297</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1919,22 +1898,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920411</v>
+        <v>22330051920298</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1942,22 +1921,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920272</v>
+        <v>22330051920302</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1965,22 +1944,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920002</v>
+        <v>22330051920303</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1988,7 +1967,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920205</v>
+        <v>22330051920307</v>
       </c>
       <c r="B34" t="s">
         <v>48</v>
@@ -1997,13 +1976,13 @@
         <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2011,22 +1990,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920423</v>
+        <v>22330051920308</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2034,22 +2013,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920374</v>
+        <v>22330051920311</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2057,22 +2033,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920222</v>
+        <v>22330051920370</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2080,90 +2056,24 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>22330051920307</v>
+        <v>21330051920114</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>22330051920311</v>
-      </c>
-      <c r="B39" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>22330051920370</v>
-      </c>
-      <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920114</v>
-      </c>
-      <c r="B41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" t="s">
-        <v>79</v>
-      </c>
-      <c r="D41" t="s">
-        <v>117</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="112">
   <si>
     <t>Mat</t>
   </si>
@@ -85,57 +85,66 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VERA</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>OLMEDO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -145,12 +154,6 @@
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>CESAR</t>
   </si>
   <si>
@@ -166,9 +169,6 @@
     <t>LUNA</t>
   </si>
   <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
     <t>PUGA CABRERA</t>
   </si>
   <si>
@@ -178,129 +178,147 @@
     <t>CERON</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
     <t>GERARDO</t>
   </si>
   <si>
+    <t>------</t>
+  </si>
+  <si>
     <t>CASASOLA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>VALLEJO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>CADENA</t>
   </si>
   <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
     <t>CARBAJAL</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>ISRAEL</t>
+    <t>DAVID</t>
   </si>
   <si>
     <t>ERIK</t>
   </si>
   <si>
+    <t>MIA</t>
+  </si>
+  <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>KEVIN RAUL</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
     <t>SERGIO FARITH</t>
   </si>
   <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
     <t>QUETZALY</t>
   </si>
   <si>
@@ -313,12 +331,6 @@
     <t>DANA PAOLA</t>
   </si>
   <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
     <t>LUIS GUSTAVO</t>
   </si>
   <si>
@@ -331,16 +343,7 @@
     <t>JOSE CARMELO</t>
   </si>
   <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
     <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -1231,16 +1234,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920371</v>
+        <v>22330051920188</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1260,10 +1263,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1277,16 +1280,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920262</v>
+        <v>22330051920263</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1300,16 +1303,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920262</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1323,16 +1326,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920367</v>
+        <v>22330051920409</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1346,16 +1349,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920276</v>
+        <v>22330051920265</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1369,22 +1372,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920362</v>
+        <v>22330051920411</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1392,22 +1395,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920394</v>
+        <v>22330051920276</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1415,22 +1418,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920419</v>
+        <v>22330051920282</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1438,22 +1441,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920312</v>
+        <v>22330051920374</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1461,22 +1464,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920397</v>
+        <v>22330051920222</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1484,22 +1487,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920152</v>
+        <v>22330051920425</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1507,160 +1510,160 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920177</v>
+        <v>22330051920302</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920188</v>
+        <v>22330051920303</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920187</v>
+        <v>22330051920308</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920192</v>
+        <v>22330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920363</v>
+        <v>22330051920397</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920409</v>
+        <v>20330051920152</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920411</v>
+        <v>22330051920177</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1668,22 +1671,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920272</v>
+        <v>22330051920187</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1691,22 +1694,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920285</v>
+        <v>22330051920192</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1714,22 +1717,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920002</v>
+        <v>22330051920363</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1737,22 +1740,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920205</v>
+        <v>22330051920272</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1760,22 +1763,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920423</v>
+        <v>22330051920367</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1783,22 +1786,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920374</v>
+        <v>22330051920285</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1806,16 +1809,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920222</v>
+        <v>21330051920002</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1829,22 +1832,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920294</v>
+        <v>22330051920205</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1852,22 +1855,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920412</v>
+        <v>22330051920394</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1875,22 +1878,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920297</v>
+        <v>22330051920423</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1898,16 +1901,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920298</v>
+        <v>22330051920294</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -1921,16 +1924,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920302</v>
+        <v>22330051920412</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -1944,16 +1947,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920303</v>
+        <v>22330051920297</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -1967,16 +1970,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920307</v>
+        <v>22330051920298</v>
       </c>
       <c r="B34" t="s">
         <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -1990,16 +1993,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920308</v>
+        <v>22330051920307</v>
       </c>
       <c r="B35" t="s">
         <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2019,7 +2022,7 @@
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2039,10 +2042,10 @@
         <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -2062,10 +2065,10 @@
         <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="100">
   <si>
     <t>Mat</t>
   </si>
@@ -97,136 +97,124 @@
     <t>BACILIO</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
   </si>
   <si>
     <t>ROCHA</t>
@@ -238,15 +226,12 @@
     <t>VALLEJO</t>
   </si>
   <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
@@ -262,9 +247,6 @@
     <t>LUIS JAVIER</t>
   </si>
   <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
@@ -274,21 +256,18 @@
     <t>SAUL KOURCHENKOV</t>
   </si>
   <si>
+    <t>ASHLEY</t>
+  </si>
+  <si>
     <t>KARLA YARITZY</t>
   </si>
   <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>KEVIN RAUL</t>
+    <t>EFRAIN DE JESUS</t>
   </si>
   <si>
     <t>ABDIEL ARMANDO</t>
   </si>
   <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -304,22 +283,19 @@
     <t>MARCO</t>
   </si>
   <si>
-    <t>HECTOR ALAN</t>
-  </si>
-  <si>
     <t>ERIK OMAR</t>
   </si>
   <si>
     <t>OSMAR</t>
   </si>
   <si>
-    <t>ALDO</t>
-  </si>
-  <si>
     <t>SERGIO FARITH</t>
   </si>
   <si>
-    <t>QUETZALY</t>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
   </si>
   <si>
     <t>ADRIAN</t>
@@ -328,28 +304,16 @@
     <t>EMILIANO GERARDO</t>
   </si>
   <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
     <t>LUIS GUSTAVO</t>
   </si>
   <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
     <t>JOSUE ISRAEL</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
     <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -805,16 +769,16 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>11</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H4">
         <v>6.8</v>
@@ -922,16 +886,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H2">
+        <v>4.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -945,16 +912,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>36.67</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -968,16 +938,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>76.47</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -991,16 +964,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>63.64</v>
+      </c>
+      <c r="H5">
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1014,16 +990,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
@@ -1079,16 +1058,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1114,7 +1093,7 @@
         <v>36.67</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1128,19 +1107,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>64.70999999999999</v>
+        <v>76.47</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1157,16 +1136,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1183,13 +1162,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H6">
         <v>6.1</v>
@@ -1202,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1240,10 +1219,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1263,10 +1242,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1286,10 +1265,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1309,10 +1288,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1326,16 +1305,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920409</v>
+        <v>22330051920265</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1349,16 +1328,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920265</v>
+        <v>22330051920411</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1372,16 +1351,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920411</v>
+        <v>22330051920276</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1395,13 +1374,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920276</v>
+        <v>22330051920282</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>78</v>
@@ -1418,22 +1397,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920282</v>
+        <v>22321052600528</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1447,10 +1426,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1464,22 +1443,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920222</v>
+        <v>22330051920291</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1487,22 +1466,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920425</v>
+        <v>22330051920302</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1510,16 +1489,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920302</v>
+        <v>22330051920308</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1533,16 +1512,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920303</v>
+        <v>22330051920312</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1556,16 +1535,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920308</v>
+        <v>22330051920397</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1579,22 +1558,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920312</v>
+        <v>20330051920152</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1602,62 +1581,62 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920397</v>
+        <v>22330051920177</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920152</v>
+        <v>22330051920192</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920177</v>
+        <v>22330051920363</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1671,22 +1650,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920187</v>
+        <v>22330051920367</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1694,22 +1673,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920192</v>
+        <v>22330051920273</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1717,22 +1696,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920363</v>
+        <v>22330051920288</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1740,22 +1719,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920272</v>
+        <v>21330051920002</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1763,22 +1742,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920367</v>
+        <v>22330051920205</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1786,22 +1765,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920285</v>
+        <v>22330051920394</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1809,22 +1788,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920002</v>
+        <v>22330051920294</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1832,22 +1811,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920205</v>
+        <v>22330051920307</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1855,22 +1834,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920394</v>
+        <v>22330051920370</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1878,22 +1857,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920423</v>
+        <v>22330051920314</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1901,182 +1880,24 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920294</v>
+        <v>21330051920114</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920412</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920297</v>
-      </c>
-      <c r="B33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920298</v>
-      </c>
-      <c r="B34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920307</v>
-      </c>
-      <c r="B35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920311</v>
-      </c>
-      <c r="B36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920370</v>
-      </c>
-      <c r="B37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920114</v>
-      </c>
-      <c r="B38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="106">
   <si>
     <t>Mat</t>
   </si>
@@ -88,57 +88,63 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>BACILIO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
@@ -166,66 +172,69 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
     <t>GERARDO</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
   </si>
   <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
@@ -238,70 +247,79 @@
     <t>DAVID</t>
   </si>
   <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
+    <t>ASHLEY</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
     <t>ERIK</t>
   </si>
   <si>
-    <t>MIA</t>
-  </si>
-  <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
     <t>KATIA PAOLA</t>
   </si>
   <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>ASHLEY</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>LUIS GUSTAVO</t>
@@ -1181,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1219,10 +1237,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1236,16 +1254,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920202</v>
+        <v>22330051920371</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1265,10 +1283,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1282,16 +1300,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920262</v>
+        <v>22330051920265</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1305,16 +1323,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1328,16 +1346,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920411</v>
+        <v>22330051920282</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1351,22 +1369,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920276</v>
+        <v>22321052600528</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1374,22 +1392,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920282</v>
+        <v>22330051920374</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1397,22 +1415,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22321052600528</v>
+        <v>22330051920302</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1420,22 +1438,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920374</v>
+        <v>22330051920308</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1443,16 +1461,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920291</v>
+        <v>22330051920312</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1466,16 +1484,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920302</v>
+        <v>22330051920397</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1489,22 +1507,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920308</v>
+        <v>21330051920122</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1512,22 +1530,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920312</v>
+        <v>20330051920152</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1535,62 +1553,62 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920397</v>
+        <v>22330051920177</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920152</v>
+        <v>22330051920192</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920177</v>
+        <v>22330051920363</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1604,16 +1622,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920192</v>
+        <v>22330051920202</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1627,22 +1645,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920363</v>
+        <v>22330051920262</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1650,16 +1668,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920367</v>
+        <v>22330051920411</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1673,7 +1691,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920273</v>
+        <v>22330051920367</v>
       </c>
       <c r="B22" t="s">
         <v>39</v>
@@ -1682,7 +1700,7 @@
         <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1696,7 +1714,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920288</v>
+        <v>22330051920273</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
@@ -1705,7 +1723,7 @@
         <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1719,7 +1737,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920002</v>
+        <v>22330051920276</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
@@ -1728,13 +1746,13 @@
         <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1742,22 +1760,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920205</v>
+        <v>22330051920288</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
         <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1765,16 +1783,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920394</v>
+        <v>21330051920002</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
         <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1788,22 +1806,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920294</v>
+        <v>22330051920205</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1811,22 +1829,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920307</v>
+        <v>22330051920394</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1834,16 +1852,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920370</v>
+        <v>22330051920291</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -1857,16 +1875,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920314</v>
+        <v>22330051920294</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -1880,24 +1898,93 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
+        <v>22330051920307</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>22330051920370</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>22330051920314</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
         <v>21330051920114</v>
       </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" t="s">
-        <v>99</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" t="s">
         <v>10</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F34" t="s">
         <v>15</v>
       </c>
-      <c r="G31">
+      <c r="G34">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="120">
   <si>
     <t>Mat</t>
   </si>
@@ -91,78 +91,93 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>LUNA</t>
   </si>
   <si>
     <t>QUESADA</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
@@ -172,72 +187,81 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
   </si>
   <si>
     <t>OLGUIN</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -250,91 +274,109 @@
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>ASHLEY</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
+    <t>LUIS JAVIER</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>JOSE</t>
   </si>
   <si>
     <t>SAUL KOURCHENKOV</t>
   </si>
   <si>
-    <t>ASHLEY</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
   </si>
   <si>
     <t>JARED DE JESUS</t>
   </si>
   <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
     <t>AZUL MARIAM</t>
   </si>
   <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1237,10 +1279,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1260,10 +1302,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1277,16 +1319,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1300,16 +1342,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1323,16 +1365,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920270</v>
+        <v>22330051920265</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1346,16 +1388,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920282</v>
+        <v>22330051920405</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1369,22 +1411,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22321052600528</v>
+        <v>22330051920270</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1392,16 +1434,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920374</v>
+        <v>22321052600528</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1415,22 +1457,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920302</v>
+        <v>22330051920374</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1438,16 +1480,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920308</v>
+        <v>22330051920302</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1461,16 +1503,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920312</v>
+        <v>22330051920308</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1484,16 +1526,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920397</v>
+        <v>22330051920408</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1507,16 +1549,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920122</v>
+        <v>21330051920111</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -1530,16 +1572,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920152</v>
+        <v>21330051920391</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -1553,39 +1595,39 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920177</v>
+        <v>20330051920152</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920192</v>
+        <v>22330051920177</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1599,16 +1641,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920363</v>
+        <v>22330051920192</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1622,16 +1664,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920202</v>
+        <v>22330051920363</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1645,22 +1687,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920262</v>
+        <v>22330051920202</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1668,16 +1710,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920411</v>
+        <v>22330051920263</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1691,16 +1733,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920367</v>
+        <v>22330051920262</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1714,16 +1756,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920273</v>
+        <v>22330051920411</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1737,16 +1779,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920276</v>
+        <v>22330051920367</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1760,16 +1802,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920288</v>
+        <v>22330051920273</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1783,22 +1825,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920002</v>
+        <v>22330051920276</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1806,22 +1848,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920205</v>
+        <v>22330051920282</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1829,22 +1871,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920394</v>
+        <v>22330051920288</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1852,22 +1894,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920291</v>
+        <v>21330051920002</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1875,22 +1917,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920294</v>
+        <v>22330051920205</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1898,22 +1940,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920307</v>
+        <v>22330051920394</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1921,16 +1963,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920370</v>
+        <v>22330051920291</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -1944,16 +1986,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920314</v>
+        <v>22330051920294</v>
       </c>
       <c r="B33" t="s">
         <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D33" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -1967,24 +2009,162 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920114</v>
+        <v>22330051920307</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>22330051920312</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>22330051920370</v>
+      </c>
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>22330051920397</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" t="s">
+        <v>116</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>22330051920314</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" t="s">
+        <v>117</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920114</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" t="s">
         <v>10</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F39" t="s">
         <v>15</v>
       </c>
-      <c r="G34">
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920122</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="130">
   <si>
     <t>Mat</t>
   </si>
@@ -88,96 +88,105 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>PANTOJA</t>
   </si>
   <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
@@ -187,81 +196,90 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>MEDINA</t>
   </si>
   <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
     <t>JORGE</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
     <t>TELLEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -271,22 +289,82 @@
     <t>DAVID</t>
   </si>
   <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>LUIS JAVIER</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
   </si>
   <si>
-    <t>MARIA DE LOS ANGELES</t>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>ASHLEY</t>
@@ -295,79 +373,31 @@
     <t>KARLA YARITZY</t>
   </si>
   <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
     <t>ABDIEL ARMANDO</t>
   </si>
   <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
   </si>
   <si>
     <t>GUILLERMO ALEXANDER</t>
@@ -1241,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1279,10 +1309,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1296,16 +1326,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920371</v>
+        <v>22330051920193</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1319,22 +1349,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920396</v>
+        <v>22330051920371</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1351,7 +1381,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1371,10 +1401,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1388,16 +1418,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920405</v>
+        <v>22330051920270</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1411,16 +1441,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920270</v>
+        <v>22330051920395</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1434,22 +1464,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22321052600528</v>
+        <v>21330051920111</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1457,22 +1487,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920374</v>
+        <v>21330051920391</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1480,22 +1510,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920302</v>
+        <v>20330051920152</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1503,131 +1533,131 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920308</v>
+        <v>22330051920177</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920408</v>
+        <v>22330051920359</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920111</v>
+        <v>22330051920192</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920391</v>
+        <v>22330051920363</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920152</v>
+        <v>22330051920201</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920177</v>
+        <v>22330051920202</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1641,22 +1671,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920192</v>
+        <v>21330051920396</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1664,22 +1694,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920363</v>
+        <v>22330051920263</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1687,22 +1717,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920202</v>
+        <v>22330051920262</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1710,16 +1740,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920263</v>
+        <v>22330051920411</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1733,16 +1763,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920262</v>
+        <v>22330051920405</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1756,16 +1786,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920411</v>
+        <v>22330051920367</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1779,16 +1809,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920367</v>
+        <v>22330051920273</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1802,16 +1832,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920273</v>
+        <v>22330051920276</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1825,16 +1855,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920276</v>
+        <v>22330051920282</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1848,16 +1878,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920282</v>
+        <v>22330051920288</v>
       </c>
       <c r="B27" t="s">
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1871,22 +1901,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920288</v>
+        <v>21330051920002</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1894,16 +1924,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920002</v>
+        <v>22330051920205</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -1917,16 +1947,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920205</v>
+        <v>22321052600528</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -1946,10 +1976,10 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -1963,22 +1993,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920291</v>
+        <v>22330051920374</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1986,16 +2016,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920294</v>
+        <v>22330051920291</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2009,16 +2039,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920307</v>
+        <v>22330051920294</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2032,16 +2062,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920312</v>
+        <v>22330051920302</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2055,16 +2085,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920370</v>
+        <v>22330051920307</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2078,16 +2108,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920397</v>
+        <v>22330051920308</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -2101,16 +2131,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>22330051920314</v>
+        <v>22330051920312</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2124,22 +2154,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920114</v>
+        <v>22330051920370</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2147,24 +2177,116 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
+        <v>22330051920397</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>22330051920408</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>22330051920314</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920114</v>
+      </c>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" t="s">
+        <v>128</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
         <v>21330051920122</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B44" t="s">
         <v>22</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C44" t="s">
         <v>47</v>
       </c>
-      <c r="D40" t="s">
-        <v>119</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="D44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E44" t="s">
         <v>10</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F44" t="s">
         <v>15</v>
       </c>
-      <c r="G40">
+      <c r="G44">
         <v>1</v>
       </c>
     </row>
